--- a/dev/company-crew-dev/crew_specs/persona_generate.xlsx
+++ b/dev/company-crew-dev/crew_specs/persona_generate.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jck/WORK/DEV/company-crewai-amp-v2/dev/company-crew-dev/crew_specs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5FCFE78-81AE-A74B-A3BF-0E298DC1EBA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3162865-D6D0-DF4E-AE45-DB15231B8DB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{1B6F41E7-F757-EF41-AEAE-051A461303B9}"/>
   </bookViews>
@@ -305,24 +305,25 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">입력 받은 업무 목적 (business_goal) {business_goal} , 단계별 tool 유형 (step_tools) {step_tools} 을 기준으로  crewai agent 에서 필요한 config jsonc (task.jsonc, agent.jsonc) 을 만들기 위한 spec 파일을 생성한다.  
-Step_tools 은  step:tool 의 json 형태로 구성되고 tool 은 없을 수도 있으며 mcp_tool 과 연결된다. 
+    <t>사용자가 입력한 business_goal, step_tools 을 잘 이해하고 crewai agent 가 만들어질 수 있도록 각 세부 속성을 자동으로 만들어야 한다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>crewai 프레임워크, sdk 를 잘 이해하고 sdk 기반으로 실제 agent 를 작성한 경험이 풍부하다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>task_name,  task_context, task_description, task_expected_output, task_output_file, task_agent, agent_role, agent_goal, agent_backstory, agent_tools 을  markdown 표 형태로  출력</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">입력 받은 업무 목적 (business_goal) "{business_goal}" , 단계별 tool 유형 (step_tools) "{step_tools}" 을 기준으로  crewai agent 에서 필요한 config jsonc (task.jsonc, agent.jsonc) 을 만들기 위한 spec 파일을 생성한다.  
+Step_tools 은  step:tool 의 리스트 형태로 구성되고 tool 은 mcp_tool 과 연결되며, 없을 수도 있다. 
 Spec 파일의 행은 step 별로 작성되어야 한다. 
 각 step 의 명칭과 업무목적을 조합해서 task_name 을 명명한다. 
+각 step 과 도구를 조합해서  mcp tool list 를 조회하여 연관된 tool 을 agent_tools 로 설정한다. 
 그외 task, agent 에서 필요한 속성은  각각 task_xxxx,  agent_xxxx 형태로 정의하고,  해당 내용은 crewai sdk 에서 인식될 수 있도록  자동으로 작성한다.
 </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>사용자가 입력한 business_goal, step_tools 을 잘 이해하고 crewai agent 가 만들어질 수 있도록 각 세부 속성을 자동으로 만들어야 한다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>crewai 프레임워크, sdk 를 잘 이해하고 sdk 기반으로 실제 agent 를 작성한 경험이 풍부하다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>task_name,  task_context, task_description, task_expected_output, task_output_file, task_agent, agent_role, agent_goal, agent_backstory, agent_tools 을  markdown 표 형태로  출력</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -905,10 +906,10 @@
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>48</v>
@@ -920,10 +921,10 @@
         <v>50</v>
       </c>
       <c r="H2" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="I2" s="2" t="s">
         <v>52</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>53</v>
       </c>
       <c r="J2" s="4"/>
       <c r="K2" s="4"/>

--- a/dev/company-crew-dev/crew_specs/persona_generate.xlsx
+++ b/dev/company-crew-dev/crew_specs/persona_generate.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jck/WORK/DEV/company-crewai-amp-v2/dev/company-crew-dev/crew_specs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3162865-D6D0-DF4E-AE45-DB15231B8DB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A970FC0-B6A7-B447-8005-6F090FE6D388}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{1B6F41E7-F757-EF41-AEAE-051A461303B9}"/>
   </bookViews>
@@ -301,10 +301,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>crewai 프레임워크에서 필요한 config 파일을 작성한다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>사용자가 입력한 business_goal, step_tools 을 잘 이해하고 crewai agent 가 만들어질 수 있도록 각 세부 속성을 자동으로 만들어야 한다.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -320,10 +316,14 @@
     <t xml:space="preserve">입력 받은 업무 목적 (business_goal) "{business_goal}" , 단계별 tool 유형 (step_tools) "{step_tools}" 을 기준으로  crewai agent 에서 필요한 config jsonc (task.jsonc, agent.jsonc) 을 만들기 위한 spec 파일을 생성한다.  
 Step_tools 은  step:tool 의 리스트 형태로 구성되고 tool 은 mcp_tool 과 연결되며, 없을 수도 있다. 
 Spec 파일의 행은 step 별로 작성되어야 한다. 
-각 step 의 명칭과 업무목적을 조합해서 task_name 을 명명한다. 
-각 step 과 도구를 조합해서  mcp tool list 를 조회하여 연관된 tool 을 agent_tools 로 설정한다. 
-그외 task, agent 에서 필요한 속성은  각각 task_xxxx,  agent_xxxx 형태로 정의하고,  해당 내용은 crewai sdk 에서 인식될 수 있도록  자동으로 작성한다.
+. 각 step 의 명칭과 업무목적을 조합해서 task_name 을 명명한다. 
+. 각 step 과 도구를 조합해서  mcp tool list 를 조회하여 연관된 tool 을 agent_tools 로 설정한다. 
+. 그외 task, agent 에서 필요한 속성은  각각 task_xxxx,  agent_xxxx 형태로 정의하고,  해당 내용은 crewai sdk 에서 인식될 수 있도록  자동으로 작성한다.
 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>crewai spec 설계자</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -906,10 +906,10 @@
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>48</v>
@@ -918,13 +918,13 @@
         <v>49</v>
       </c>
       <c r="G2" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="H2" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="I2" s="2" t="s">
         <v>51</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>52</v>
       </c>
       <c r="J2" s="4"/>
       <c r="K2" s="4"/>

--- a/dev/company-crew-dev/crew_specs/persona_generate.xlsx
+++ b/dev/company-crew-dev/crew_specs/persona_generate.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jck/WORK/DEV/company-crewai-amp-v2/dev/company-crew-dev/crew_specs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A970FC0-B6A7-B447-8005-6F090FE6D388}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{286051CE-E696-8140-908A-DE90CE1B5EBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{1B6F41E7-F757-EF41-AEAE-051A461303B9}"/>
   </bookViews>
@@ -309,21 +309,32 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>task_name,  task_context, task_description, task_expected_output, task_output_file, task_agent, agent_role, agent_goal, agent_backstory, agent_tools 을  markdown 표 형태로  출력</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">입력 받은 업무 목적 (business_goal) "{business_goal}" , 단계별 tool 유형 (step_tools) "{step_tools}" 을 기준으로  crewai agent 에서 필요한 config jsonc (task.jsonc, agent.jsonc) 을 만들기 위한 spec 파일을 생성한다.  
-Step_tools 은  step:tool 의 리스트 형태로 구성되고 tool 은 mcp_tool 과 연결되며, 없을 수도 있다. 
+    <t>crewai spec 설계자</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>task_name,  task_context, task_description, task_expected_output, task_output_file, task_agent, agent_role, agent_goal, agent_backstory, mcp을  markdown 표 형태로  출력</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">입력 받은 페르소나 이름 (persona_name) {persona_name}, 업무 목적 (business_goal) "{business_goal}" , 단계별 tool 유형 (step_tools) "{step_tools}" 을 기준으로  crewai agent 에서 필요한 config jsonc (task.jsonc, agent.jsonc) 을 만들기 위한 spec 파일을 생성한다.  
+step_tools 은  step:tool_list 의 리스트 형태로 구성되고 각각의 tool 은 mcp와 연결되며, 연결된 tool 은 없을 수도 있다. 아래 예시를 참조해줘.
+  "step_tools": [
+    "extract:[database,datadog]",
+    "analysis",
+    "report"
+  ]  
+위 정보를 토대로 crewai config 속성을 작성해줘
+. crew_name :  persona_name 을 영어로 번역하여 설정 (markdown 문서의 이름)
+. mcp : step 과 tool 을 조합하여  mcp api 에서 가져와서 매칭  
+. task_name : 각 step 의 명칭과 업무목적을 조합해서 task_name 을 명명
 Spec 파일의 행은 step 별로 작성되어야 한다. 
-. 각 step 의 명칭과 업무목적을 조합해서 task_name 을 명명한다. 
-. 각 step 과 도구를 조합해서  mcp tool list 를 조회하여 연관된 tool 을 agent_tools 로 설정한다. 
-. 그외 task, agent 에서 필요한 속성은  각각 task_xxxx,  agent_xxxx 형태로 정의하고,  해당 내용은 crewai sdk 에서 인식될 수 있도록  자동으로 작성한다.
+. 그외 task, agent 에서 필요한 속성은  각각 task_xxxx,  agent_xxxx 형태로 정의하고,  해당 내용은 crewai sdk 에서 인식될 수 있도록  자동으로 작성한다.  
+* mcp api 
+- Endpoint: GET /api/v1/mcp/tools
+- Content-Type: application/json
+- 설명: 서버에 등록되어 있는 모든 MCP 도구(Plugin)의 메타데이터 카탈로그(name, description, input_schema, output_schema) 목록을 반환합니다.
 </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>crewai spec 설계자</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -900,16 +911,16 @@
         <v>33</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="199" customHeight="1">
+    <row r="2" spans="1:12" ht="409" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>47</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>53</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>52</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>48</v>
@@ -918,7 +929,7 @@
         <v>49</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>50</v>

--- a/dev/company-crew-dev/crew_specs/persona_generate.xlsx
+++ b/dev/company-crew-dev/crew_specs/persona_generate.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jck/WORK/DEV/company-crewai-amp-v2/dev/company-crew-dev/crew_specs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{286051CE-E696-8140-908A-DE90CE1B5EBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1ECCB484-A8CC-3E4B-A90F-30B6391E5691}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{1B6F41E7-F757-EF41-AEAE-051A461303B9}"/>
   </bookViews>
@@ -317,7 +317,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">입력 받은 페르소나 이름 (persona_name) {persona_name}, 업무 목적 (business_goal) "{business_goal}" , 단계별 tool 유형 (step_tools) "{step_tools}" 을 기준으로  crewai agent 에서 필요한 config jsonc (task.jsonc, agent.jsonc) 을 만들기 위한 spec 파일을 생성한다.  
+    <t xml:space="preserve">입력 받은 페르소나 이름 (persona_name) "{persona_name}", 업무 목적 (business_goal) "{business_goal}" , 단계별 tool 유형 (step_tools) "{step_tools}" 을 기준으로  crewai agent 에서 필요한 config jsonc (task.jsonc, agent.jsonc) 을 만들기 위한 spec 파일을 생성한다.  
 step_tools 은  step:tool_list 의 리스트 형태로 구성되고 각각의 tool 은 mcp와 연결되며, 연결된 tool 은 없을 수도 있다. 아래 예시를 참조해줘.
   "step_tools": [
     "extract:[database,datadog]",

--- a/dev/company-crew-dev/crew_specs/persona_generate.xlsx
+++ b/dev/company-crew-dev/crew_specs/persona_generate.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jck/WORK/DEV/company-crewai-amp-v2/dev/company-crew-dev/crew_specs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1ECCB484-A8CC-3E4B-A90F-30B6391E5691}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{880449CA-FBDA-264C-88C3-D45286D14531}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{1B6F41E7-F757-EF41-AEAE-051A461303B9}"/>
   </bookViews>
@@ -84,7 +84,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="56">
   <si>
     <t>task_name</t>
   </si>
@@ -301,10 +301,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>사용자가 입력한 business_goal, step_tools 을 잘 이해하고 crewai agent 가 만들어질 수 있도록 각 세부 속성을 자동으로 만들어야 한다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>crewai 프레임워크, sdk 를 잘 이해하고 sdk 기반으로 실제 agent 를 작성한 경험이 풍부하다.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -314,6 +310,15 @@
   </si>
   <si>
     <t>task_name,  task_context, task_description, task_expected_output, task_output_file, task_agent, agent_role, agent_goal, agent_backstory, mcp을  markdown 표 형태로  출력</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>사용자가 입력한 persona_name, business_goal, step_tools 을 잘 이해하고 crewai agent 가 만들어질 수 있도록 각 세부 속성을 자동으로 만들어야 한다. 
+Crew spec 문서는 한글로 만들어야 한다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>all.mcp.list</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -326,15 +331,10 @@
   ]  
 위 정보를 토대로 crewai config 속성을 작성해줘
 . crew_name :  persona_name 을 영어로 번역하여 설정 (markdown 문서의 이름)
-. mcp : step 과 tool 을 조합하여  mcp api 에서 가져와서 매칭  
-. task_name : 각 step 의 명칭과 업무목적을 조합해서 task_name 을 명명
+. mcp : step 과 tool명 을 조합하고 all.mcp.list tool 에서 mcp_name (response.tools.name)을 가져와서 매칭  
+. task_name : 각 step 의 명칭과 업무목적을 조합해서 task_name 을 명명 (반드시 영어로 작성)
 Spec 파일의 행은 step 별로 작성되어야 한다. 
-. 그외 task, agent 에서 필요한 속성은  각각 task_xxxx,  agent_xxxx 형태로 정의하고,  해당 내용은 crewai sdk 에서 인식될 수 있도록  자동으로 작성한다.  
-* mcp api 
-- Endpoint: GET /api/v1/mcp/tools
-- Content-Type: application/json
-- 설명: 서버에 등록되어 있는 모든 MCP 도구(Plugin)의 메타데이터 카탈로그(name, description, input_schema, output_schema) 목록을 반환합니다.
-</t>
+. 그외 task, agent 에서 필요한 속성은  각각 task_xxxx,  agent_xxxx 형태로 정의하고,  해당 내용은 crewai sdk 에서 인식될 수 있도록  자동으로 작성한다. </t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -911,16 +911,16 @@
         <v>33</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="409" customHeight="1">
+    <row r="2" spans="1:12" ht="351" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>47</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>48</v>
@@ -929,15 +929,17 @@
         <v>49</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H2" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="I2" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="I2" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="J2" s="4"/>
+      <c r="J2" s="4" t="s">
+        <v>54</v>
+      </c>
       <c r="K2" s="4"/>
     </row>
   </sheetData>

--- a/dev/company-crew-dev/crew_specs/persona_generate.xlsx
+++ b/dev/company-crew-dev/crew_specs/persona_generate.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jck/WORK/DEV/company-crewai-amp-v2/dev/company-crew-dev/crew_specs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{880449CA-FBDA-264C-88C3-D45286D14531}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A08257BF-AE23-EE4F-A33D-B78F33093703}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{1B6F41E7-F757-EF41-AEAE-051A461303B9}"/>
   </bookViews>
@@ -322,7 +322,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">입력 받은 페르소나 이름 (persona_name) "{persona_name}", 업무 목적 (business_goal) "{business_goal}" , 단계별 tool 유형 (step_tools) "{step_tools}" 을 기준으로  crewai agent 에서 필요한 config jsonc (task.jsonc, agent.jsonc) 을 만들기 위한 spec 파일을 생성한다.  
+    <t>입력 받은 페르소나 이름 (persona_name) "{persona_name}", 업무 목적 (business_goal) "{business_goal}" , 단계별 tool 유형 (step_tools) "{step_tools}" 을 기준으로  crewai agent 에서 필요한 config jsonc (task.jsonc, agent.jsonc) 을 만들기 위한 spec 파일을 생성한다.  spec 파일은  step 별로 task 로 매칭되어 각 행라인으로 작성한다.
 step_tools 은  step:tool_list 의 리스트 형태로 구성되고 각각의 tool 은 mcp와 연결되며, 연결된 tool 은 없을 수도 있다. 아래 예시를 참조해줘.
   "step_tools": [
     "extract:[database,datadog]",
@@ -331,10 +331,11 @@
   ]  
 위 정보를 토대로 crewai config 속성을 작성해줘
 . crew_name :  persona_name 을 영어로 번역하여 설정 (markdown 문서의 이름)
-. mcp : step 과 tool명 을 조합하고 all.mcp.list tool 에서 mcp_name (response.tools.name)을 가져와서 매칭  
-. task_name : 각 step 의 명칭과 업무목적을 조합해서 task_name 을 명명 (반드시 영어로 작성)
-Spec 파일의 행은 step 별로 작성되어야 한다. 
-. 그외 task, agent 에서 필요한 속성은  각각 task_xxxx,  agent_xxxx 형태로 정의하고,  해당 내용은 crewai sdk 에서 인식될 수 있도록  자동으로 작성한다. </t>
+. task_name : 각 step 의 명칭과 업무목적을 조합해서 단위 프로세스를 명명 (반드시 영어로 작성) 
+. task_context : 이전 step 과 연결될 경우 이전 task_name 을 그대로 작성
+. task_agent : 각 step 의 명칭과 업무목적을 조합해서 수행하는 역할자 설정 (반드시 영어로 작성)
+. mcp : step 과 tool명 을 조합하고 all.mcp.list tool 에서 mcp_name (response.tools.name)을 가져와서 매칭   
+. 그외 task, agent 에서 필요한 속성은  각각 task_xxxx,  agent_xxxx 형태로 정의하고,  해당 내용은 crewai sdk 에서 인식될 수 있도록  자동으로 작성한다. (한글로 작성)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -911,7 +912,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="351" customHeight="1">
+    <row r="2" spans="1:12" ht="375" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>47</v>
       </c>

--- a/dev/company-crew-dev/crew_specs/persona_generate.xlsx
+++ b/dev/company-crew-dev/crew_specs/persona_generate.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10821"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10920"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jck/WORK/DEV/company-crewai-amp-v2/dev/company-crew-dev/crew_specs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A08257BF-AE23-EE4F-A33D-B78F33093703}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CE2CD56-70DD-5E4B-8C54-4A5372C84792}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{1B6F41E7-F757-EF41-AEAE-051A461303B9}"/>
   </bookViews>
@@ -293,10 +293,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>./output/spec.md</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>crewai_specialist</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -319,6 +315,10 @@
   </si>
   <si>
     <t>all.mcp.list</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>./output/{crew_name}.md</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -330,7 +330,7 @@
     "report"
   ]  
 위 정보를 토대로 crewai config 속성을 작성해줘
-. crew_name :  persona_name 을 영어로 번역하여 설정 (markdown 문서의 이름)
+. crew_name :  persona_name 을 영어로 번역하여 설정 (output_file markdown 문서의 이름)
 . task_name : 각 step 의 명칭과 업무목적을 조합해서 단위 프로세스를 명명 (반드시 영어로 작성) 
 . task_context : 이전 step 과 연결될 경우 이전 task_name 을 그대로 작성
 . task_agent : 각 step 의 명칭과 업무목적을 조합해서 수행하는 역할자 설정 (반드시 영어로 작성)
@@ -865,7 +865,7 @@
     <col min="2" max="2" width="18.7109375" customWidth="1"/>
     <col min="3" max="3" width="87.42578125" customWidth="1"/>
     <col min="4" max="4" width="31.5703125" customWidth="1"/>
-    <col min="5" max="5" width="16.28515625" customWidth="1"/>
+    <col min="5" max="5" width="24.5703125" customWidth="1"/>
     <col min="6" max="6" width="20.42578125" customWidth="1"/>
     <col min="7" max="7" width="17.28515625" customWidth="1"/>
     <col min="8" max="8" width="29.85546875" customWidth="1"/>
@@ -921,25 +921,25 @@
         <v>55</v>
       </c>
       <c r="D2" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="H2" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="F2" s="3" t="s">
+      <c r="I2" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="G2" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="H2" s="2" t="s">
+      <c r="J2" s="4" t="s">
         <v>53</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="J2" s="4" t="s">
-        <v>54</v>
       </c>
       <c r="K2" s="4"/>
     </row>

--- a/dev/company-crew-dev/crew_specs/persona_generate.xlsx
+++ b/dev/company-crew-dev/crew_specs/persona_generate.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jck/WORK/DEV/company-crewai-amp-v2/dev/company-crew-dev/crew_specs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CE2CD56-70DD-5E4B-8C54-4A5372C84792}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C125044-D462-FC49-A06D-D3A387662137}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{1B6F41E7-F757-EF41-AEAE-051A461303B9}"/>
   </bookViews>
@@ -335,7 +335,8 @@
 . task_context : 이전 step 과 연결될 경우 이전 task_name 을 그대로 작성
 . task_agent : 각 step 의 명칭과 업무목적을 조합해서 수행하는 역할자 설정 (반드시 영어로 작성)
 . mcp : step 과 tool명 을 조합하고 all.mcp.list tool 에서 mcp_name (response.tools.name)을 가져와서 매칭   
-. 그외 task, agent 에서 필요한 속성은  각각 task_xxxx,  agent_xxxx 형태로 정의하고,  해당 내용은 crewai sdk 에서 인식될 수 있도록  자동으로 작성한다. (한글로 작성)</t>
+. 그외 task, agent 에서 필요한 속성은  각각 task_xxxx,  agent_xxxx 형태로 정의하고,  해당 내용은 crewai sdk 에서 인식될 수 있도록  자동으로 작성한다. (한글로 작성) 
+. crew_name 은 {crew_name} 변수로 저장하여 output_file 의 명칭으로 사용한다.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -912,7 +913,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="375" customHeight="1">
+    <row r="2" spans="1:12" ht="408" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>47</v>
       </c>

--- a/dev/company-crew-dev/crew_specs/persona_generate.xlsx
+++ b/dev/company-crew-dev/crew_specs/persona_generate.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jck/WORK/DEV/company-crewai-amp-v2/dev/company-crew-dev/crew_specs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C125044-D462-FC49-A06D-D3A387662137}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93297171-4E5C-1F44-B3F4-960CC8DE7E0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{1B6F41E7-F757-EF41-AEAE-051A461303B9}"/>
   </bookViews>
@@ -322,14 +322,14 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>입력 받은 페르소나 이름 (persona_name) "{persona_name}", 업무 목적 (business_goal) "{business_goal}" , 단계별 tool 유형 (step_tools) "{step_tools}" 을 기준으로  crewai agent 에서 필요한 config jsonc (task.jsonc, agent.jsonc) 을 만들기 위한 spec 파일을 생성한다.  spec 파일은  step 별로 task 로 매칭되어 각 행라인으로 작성한다.
+    <t>입력 받은 페르소나 이름 (persona_name) "{persona_name}", 업무 유형 (work_type) "{work_type}", 업무 목적 (business_goal) "{business_goal}" , 단계별 tool 유형 (step_tools) "{step_tools}" 을 기준으로  crewai agent 에서 필요한 config jsonc (task.jsonc, agent.jsonc) 을 만들기 위한 spec 파일을 생성한다.  spec 파일은  step 별로 task 로 매칭되어 각 행라인으로 작성한다.
 step_tools 은  step:tool_list 의 리스트 형태로 구성되고 각각의 tool 은 mcp와 연결되며, 연결된 tool 은 없을 수도 있다. 아래 예시를 참조해줘.
   "step_tools": [
     "extract:[database,datadog]",
     "analysis",
     "report"
   ]  
-위 정보를 토대로 crewai config 속성을 작성해줘
+위 work_type,  business_goal 정보를 토대로 crewai config 속성을 작성해줘
 . crew_name :  persona_name 을 영어로 번역하여 설정 (output_file markdown 문서의 이름)
 . task_name : 각 step 의 명칭과 업무목적을 조합해서 단위 프로세스를 명명 (반드시 영어로 작성) 
 . task_context : 이전 step 과 연결될 경우 이전 task_name 을 그대로 작성

--- a/dev/company-crew-dev/crew_specs/persona_generate.xlsx
+++ b/dev/company-crew-dev/crew_specs/persona_generate.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jck/WORK/DEV/company-crewai-amp-v2/dev/company-crew-dev/crew_specs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93297171-4E5C-1F44-B3F4-960CC8DE7E0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3E2B4EC-6FF6-6B4F-A95B-8078E54B62B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{1B6F41E7-F757-EF41-AEAE-051A461303B9}"/>
   </bookViews>
@@ -336,7 +336,7 @@
 . task_agent : 각 step 의 명칭과 업무목적을 조합해서 수행하는 역할자 설정 (반드시 영어로 작성)
 . mcp : step 과 tool명 을 조합하고 all.mcp.list tool 에서 mcp_name (response.tools.name)을 가져와서 매칭   
 . 그외 task, agent 에서 필요한 속성은  각각 task_xxxx,  agent_xxxx 형태로 정의하고,  해당 내용은 crewai sdk 에서 인식될 수 있도록  자동으로 작성한다. (한글로 작성) 
-. crew_name 은 {crew_name} 변수로 저장하여 output_file 의 명칭으로 사용한다.</t>
+. crew_name 은 변수로 저장하여 output_file 의 명칭으로 사용한다.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>

--- a/dev/company-crew-dev/crew_specs/persona_generate.xlsx
+++ b/dev/company-crew-dev/crew_specs/persona_generate.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10920"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10927"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jck/WORK/DEV/company-crewai-amp-v2/dev/company-crew-dev/crew_specs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3E2B4EC-6FF6-6B4F-A95B-8078E54B62B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1373E19-0217-D247-89D3-FCFE0C5B2775}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{1B6F41E7-F757-EF41-AEAE-051A461303B9}"/>
   </bookViews>
@@ -309,11 +309,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>사용자가 입력한 persona_name, business_goal, step_tools 을 잘 이해하고 crewai agent 가 만들어질 수 있도록 각 세부 속성을 자동으로 만들어야 한다. 
-Crew spec 문서는 한글로 만들어야 한다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>all.mcp.list</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -322,21 +317,26 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>입력 받은 페르소나 이름 (persona_name) "{persona_name}", 업무 유형 (work_type) "{work_type}", 업무 목적 (business_goal) "{business_goal}" , 단계별 tool 유형 (step_tools) "{step_tools}" 을 기준으로  crewai agent 에서 필요한 config jsonc (task.jsonc, agent.jsonc) 을 만들기 위한 spec 파일을 생성한다.  spec 파일은  step 별로 task 로 매칭되어 각 행라인으로 작성한다.
-step_tools 은  step:tool_list 의 리스트 형태로 구성되고 각각의 tool 은 mcp와 연결되며, 연결된 tool 은 없을 수도 있다. 아래 예시를 참조해줘.
+    <t>입력 받은 페르소나 이름 (persona_name) "{persona_name}", 업무 유형 (work_type) "{work_type}", 업무 목적 (business_goal) "{business_goal}" , 단계별 tool 유형 (step_tools) "{step_tools}" 을 기준으로  crewai agent 에서 필요한 config jsonc (task.jsonc, agent.jsonc) 을 만들기 위한 spec 파일을 생성합니다.  spec 파일은  step 별로 task 로 매칭되어 각 행라인으로 작성합니다.
+step_tools 은  step:tool_list 의 리스트 형태로 구성되고 각각의 tool 은 mcp와 연결되며, 연결된 tool 은 없을 수도 있습니다. 아래 예시를 참조해주세요.
   "step_tools": [
     "extract:[database,datadog]",
     "analysis",
     "report"
   ]  
-위 work_type,  business_goal 정보를 토대로 crewai config 속성을 작성해줘
+위 work_type,  business_goal 정보를 토대로 crewai config 속성을 작성해주세요.
 . crew_name :  persona_name 을 영어로 번역하여 설정 (output_file markdown 문서의 이름)
 . task_name : 각 step 의 명칭과 업무목적을 조합해서 단위 프로세스를 명명 (반드시 영어로 작성) 
 . task_context : 이전 step 과 연결될 경우 이전 task_name 을 그대로 작성
 . task_agent : 각 step 의 명칭과 업무목적을 조합해서 수행하는 역할자 설정 (반드시 영어로 작성)
 . mcp : step 과 tool명 을 조합하고 all.mcp.list tool 에서 mcp_name (response.tools.name)을 가져와서 매칭   
-. 그외 task, agent 에서 필요한 속성은  각각 task_xxxx,  agent_xxxx 형태로 정의하고,  해당 내용은 crewai sdk 에서 인식될 수 있도록  자동으로 작성한다. (한글로 작성) 
-. crew_name 은 변수로 저장하여 output_file 의 명칭으로 사용한다.</t>
+. 그외 task, agent 에서 필요한 속성은  각각 task_xxxx,  agent_xxxx 형태로 정의하고,  해당 내용은 crewai sdk 에서 인식될 수 있도록  자동으로 작성해주세요. (한글로 작성) 
+. crew_name 은 변수로 저장하여 output_file 의 명칭으로 사용합니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>사용자가 입력한 persona_name, business_goal, work_type, step_tools 을 잘 이해하고 crewai agent 가 만들어질 수 있도록 각 세부 속성을 자동으로 만들어야 한다. 
+Crew spec 문서는 한글로 만들어야 한다.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -919,13 +919,13 @@
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>51</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>48</v>
@@ -934,13 +934,13 @@
         <v>50</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>49</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="K2" s="4"/>
     </row>

--- a/dev/company-crew-dev/crew_specs/persona_generate.xlsx
+++ b/dev/company-crew-dev/crew_specs/persona_generate.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jck/WORK/DEV/company-crewai-amp-v2/dev/company-crew-dev/crew_specs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1373E19-0217-D247-89D3-FCFE0C5B2775}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6628A709-1206-1248-ADBF-A5AEF818216D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{1B6F41E7-F757-EF41-AEAE-051A461303B9}"/>
   </bookViews>
@@ -313,10 +313,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>./output/{crew_name}.md</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>입력 받은 페르소나 이름 (persona_name) "{persona_name}", 업무 유형 (work_type) "{work_type}", 업무 목적 (business_goal) "{business_goal}" , 단계별 tool 유형 (step_tools) "{step_tools}" 을 기준으로  crewai agent 에서 필요한 config jsonc (task.jsonc, agent.jsonc) 을 만들기 위한 spec 파일을 생성합니다.  spec 파일은  step 별로 task 로 매칭되어 각 행라인으로 작성합니다.
 step_tools 은  step:tool_list 의 리스트 형태로 구성되고 각각의 tool 은 mcp와 연결되며, 연결된 tool 은 없을 수도 있습니다. 아래 예시를 참조해주세요.
   "step_tools": [
@@ -337,6 +333,10 @@
   <si>
     <t>사용자가 입력한 persona_name, business_goal, work_type, step_tools 을 잘 이해하고 crewai agent 가 만들어질 수 있도록 각 세부 속성을 자동으로 만들어야 한다. 
 Crew spec 문서는 한글로 만들어야 한다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>./output/crew_spec.md</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -919,13 +919,13 @@
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>51</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>48</v>
@@ -934,7 +934,7 @@
         <v>50</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>49</v>

--- a/dev/company-crew-dev/crew_specs/persona_generate.xlsx
+++ b/dev/company-crew-dev/crew_specs/persona_generate.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jck/WORK/DEV/company-crewai-amp-v2/dev/company-crew-dev/crew_specs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6628A709-1206-1248-ADBF-A5AEF818216D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B3304DD-B7E8-E04C-AFCC-2DB8145CF3BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{1B6F41E7-F757-EF41-AEAE-051A461303B9}"/>
   </bookViews>
@@ -859,7 +859,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8965F465-69CB-8643-BA15-521BEF7BAC6E}">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L3"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -944,6 +944,7 @@
       </c>
       <c r="K2" s="4"/>
     </row>
+    <row r="3" spans="1:12" ht="94" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
